--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486265_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486265_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.003299999999999</v>
+        <v>8.2943</v>
       </c>
       <c r="E2" t="n">
         <v>8.375</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6282</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>8.123900000000001</v>
@@ -610,13 +610,13 @@
         <v>2.3926</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3818</v>
+        <v>-0.3272</v>
       </c>
       <c r="T2" t="n">
         <v>-0.6934</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0751</v>
+        <v>0.3662</v>
       </c>
       <c r="V2" t="n">
         <v>2.4552</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0403</v>
+        <v>1.2753</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2555</v>
+        <v>1.3672</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2152</v>
+        <v>-0.0919</v>
       </c>
       <c r="G3" t="n">
         <v>-0.2404</v>
@@ -688,13 +688,13 @@
         <v>0.6525</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5018</v>
+        <v>-0.2668</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.137</v>
+        <v>-0.0252</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3648</v>
+        <v>-0.2415</v>
       </c>
       <c r="V3" t="n">
         <v>1.13</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.0229</v>
+        <v>-1.1424</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.9471000000000001</v>
+        <v>-1.2823</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0759</v>
+        <v>0.1399</v>
       </c>
       <c r="G4" t="n">
         <v>-1.3035</v>
@@ -766,13 +766,13 @@
         <v>1.305</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1746</v>
+        <v>-0.2941</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2139</v>
+        <v>-0.5492</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0393</v>
+        <v>0.2551</v>
       </c>
       <c r="V4" t="n">
         <v>1.3252</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. COPES</t>
+          <t>F. NWAOKORIE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.2315</v>
+        <v>-2.0596</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8061</v>
+        <v>-0.8176</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.0377</v>
+        <v>-1.242</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.6542</v>
+        <v>-2.9832</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.0612</v>
+        <v>-0.8549</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.593</v>
+        <v>-2.1284</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.8219</v>
+        <v>-0.2171</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0968</v>
+        <v>1.022</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.7251</v>
+        <v>-1.2391</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.8322</v>
+        <v>-2.7661</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9643</v>
+        <v>-1.8768</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.8679</v>
+        <v>-0.8893</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.305</v>
+        <v>0.435</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R5" t="n">
-        <v>0.87</v>
+        <v>1.5225</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9026999999999999</v>
+        <v>-0.2509</v>
       </c>
       <c r="T5" t="n">
-        <v>1.4132</v>
+        <v>-0.6429</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5105</v>
+        <v>0.392</v>
       </c>
       <c r="V5" t="n">
-        <v>2.8249</v>
+        <v>0.7395</v>
       </c>
       <c r="W5" t="n">
-        <v>3.3899</v>
+        <v>1.13</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. NWAOKORIE</t>
+          <t>F. COPES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.9285</v>
+        <v>-2.3992</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.594</v>
+        <v>0.5768</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3345</v>
+        <v>-2.976</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.9832</v>
+        <v>-3.6542</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8549</v>
+        <v>-1.0612</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.1284</v>
+        <v>-2.593</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2171</v>
+        <v>-0.8219</v>
       </c>
       <c r="K6" t="n">
-        <v>1.022</v>
+        <v>-0.0968</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.2391</v>
+        <v>-0.7251</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.7661</v>
+        <v>-2.8322</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.8768</v>
+        <v>-0.9643</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8893</v>
+        <v>-1.8679</v>
       </c>
       <c r="P6" t="n">
-        <v>0.435</v>
+        <v>-1.305</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5225</v>
+        <v>0.87</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1198</v>
+        <v>-0.265</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4194</v>
+        <v>0.1839</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2996</v>
+        <v>-0.4488</v>
       </c>
       <c r="V6" t="n">
-        <v>0.7395</v>
+        <v>2.8249</v>
       </c>
       <c r="W6" t="n">
-        <v>1.13</v>
+        <v>3.3899</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3904</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.3527</v>
+        <v>-2.7323</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4406</v>
+        <v>0.1181</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.912</v>
+        <v>-2.8504</v>
       </c>
       <c r="G7" t="n">
         <v>-0.2137</v>
@@ -1000,13 +1000,13 @@
         <v>1.305</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.139</v>
+        <v>-0.5185</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.822</v>
+        <v>-0.2632</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.317</v>
+        <v>-0.2554</v>
       </c>
       <c r="V7" t="n">
         <v>-1.13</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.7432</v>
+        <v>-3.8164</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.25</v>
+        <v>-2.1382</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4933</v>
+        <v>-1.6782</v>
       </c>
       <c r="G8" t="n">
         <v>-1.9173</v>
@@ -1078,13 +1078,13 @@
         <v>1.7401</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8683</v>
+        <v>-0.9415</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0274</v>
+        <v>-0.9157</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1591</v>
+        <v>-0.0258</v>
       </c>
       <c r="V8" t="n">
         <v>0.5649999999999999</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.9938</v>
+        <v>-5.331</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.3766</v>
+        <v>-2.9296</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.6172</v>
+        <v>-2.4014</v>
       </c>
       <c r="G9" t="n">
         <v>-2.1204</v>
@@ -1156,13 +1156,13 @@
         <v>1.9576</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.1562</v>
+        <v>-1.4934</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.3014</v>
+        <v>-0.8544</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8548</v>
+        <v>-0.639</v>
       </c>
       <c r="V9" t="n">
         <v>-1.4997</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.4337</v>
+        <v>-6.7516</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.9125</v>
+        <v>-3.3537</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.5212</v>
+        <v>-3.3979</v>
       </c>
       <c r="G10" t="n">
         <v>-3.2657</v>
@@ -1234,13 +1234,13 @@
         <v>1.305</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0174</v>
+        <v>-0.3353</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8904</v>
+        <v>-0.3317</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1269</v>
+        <v>-0.0036</v>
       </c>
       <c r="V10" t="n">
         <v>-2.2806</v>
@@ -1267,16 +1267,16 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-14.6627</v>
+        <v>-14.6629</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0842000000000005</v>
+        <v>-0.08429999999999982</v>
       </c>
       <c r="F11" t="n">
-        <v>-14.5788</v>
+        <v>-14.5786</v>
       </c>
       <c r="G11" t="n">
-        <v>-7.5745</v>
+        <v>-7.574499999999999</v>
       </c>
       <c r="H11" t="n">
         <v>0.0752000000000006</v>
@@ -1303,7 +1303,7 @@
         <v>-12.6185</v>
       </c>
       <c r="P11" t="n">
-        <v>-6.525099999999999</v>
+        <v>-6.5251</v>
       </c>
       <c r="Q11" t="n">
         <v>-19.5757</v>
@@ -1312,13 +1312,13 @@
         <v>13.0503</v>
       </c>
       <c r="S11" t="n">
-        <v>-4.692600000000001</v>
+        <v>-4.6927</v>
       </c>
       <c r="T11" t="n">
-        <v>-4.0917</v>
+        <v>-4.091799999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6009000000000001</v>
+        <v>-0.6008</v>
       </c>
       <c r="V11" t="n">
         <v>4.1295</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>10.9117</v>
+        <v>11.1468</v>
       </c>
       <c r="E12" t="n">
-        <v>7.7199</v>
+        <v>7.8316</v>
       </c>
       <c r="F12" t="n">
-        <v>3.1918</v>
+        <v>3.3151</v>
       </c>
       <c r="G12" t="n">
         <v>8.8757</v>
@@ -1390,13 +1390,13 @@
         <v>3.6976</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6662</v>
+        <v>0.9013</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1454</v>
+        <v>-0.0336</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8116</v>
+        <v>0.9349</v>
       </c>
       <c r="V12" t="n">
         <v>0.9347</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.950699999999999</v>
+        <v>9.7561</v>
       </c>
       <c r="E13" t="n">
-        <v>8.5364</v>
+        <v>9.0952</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4143</v>
+        <v>0.6609</v>
       </c>
       <c r="G13" t="n">
         <v>5.3513</v>
@@ -1468,13 +1468,13 @@
         <v>3.2626</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2706</v>
+        <v>0.5348000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.822</v>
+        <v>-0.2632</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5513</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>1.695</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1458</v>
+        <v>1.5234</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.5758</v>
+        <v>-0.3523</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7216</v>
+        <v>1.8757</v>
       </c>
       <c r="G14" t="n">
         <v>-0.7231</v>
@@ -1546,13 +1546,13 @@
         <v>2.6101</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3887</v>
+        <v>0.7664</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1454</v>
+        <v>0.0781</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5341</v>
+        <v>0.6883</v>
       </c>
       <c r="V14" t="n">
         <v>-1.13</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. GONZÁLEZ PÉREZ</t>
+          <t>L. NWOGBO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6503</v>
+        <v>0.8862</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1734</v>
+        <v>-1.0434</v>
       </c>
       <c r="F15" t="n">
-        <v>0.477</v>
+        <v>1.9296</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.893</v>
+        <v>0.6472</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.332</v>
+        <v>0.3348</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4391</v>
+        <v>0.3124</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.7566000000000001</v>
+        <v>0.9525</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.8331</v>
+        <v>0.6847</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0765</v>
+        <v>0.2677</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1364</v>
+        <v>-0.3053</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4989</v>
+        <v>-0.3499</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3626</v>
+        <v>0.0446</v>
       </c>
       <c r="P15" t="n">
-        <v>1.0875</v>
+        <v>-2.6101</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-4.3501</v>
       </c>
       <c r="R15" t="n">
-        <v>1.0875</v>
+        <v>1.7401</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1953</v>
+        <v>0.5891</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5396</v>
+        <v>-0.1009</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6558</v>
+        <v>0.6901</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.7395</v>
+        <v>2.2599</v>
       </c>
       <c r="W15" t="n">
-        <v>0.3904</v>
+        <v>2.4552</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.13</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. NWOGBO</t>
+          <t>A. GONZÁLEZ PÉREZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3261</v>
+        <v>0.1379</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.4905</v>
+        <v>0.0616</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8166</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6472</v>
+        <v>-0.893</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3348</v>
+        <v>-1.332</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3124</v>
+        <v>0.4391</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9525</v>
+        <v>-0.7566000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6847</v>
+        <v>-0.8331</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2677</v>
+        <v>0.0765</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3053</v>
+        <v>-0.1364</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3499</v>
+        <v>-0.4989</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0446</v>
+        <v>0.3626</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.6101</v>
+        <v>1.0875</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.3501</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7401</v>
+        <v>1.0875</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0291</v>
+        <v>0.6829</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.548</v>
+        <v>0.4278</v>
       </c>
       <c r="U16" t="n">
-        <v>0.577</v>
+        <v>0.2551</v>
       </c>
       <c r="V16" t="n">
-        <v>2.2599</v>
+        <v>-0.7395</v>
       </c>
       <c r="W16" t="n">
-        <v>2.4552</v>
+        <v>0.3904</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1952</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. GIOVANNETTI</t>
+          <t>M. SOLA IDRISU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.052</v>
+        <v>-0.3773</v>
       </c>
       <c r="E17" t="n">
-        <v>0.465</v>
+        <v>-0.8525</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.413</v>
+        <v>0.4752</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.9794</v>
+        <v>-0.2768</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5626</v>
+        <v>-0.1277</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.5419</v>
+        <v>-0.149</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4734</v>
+        <v>-0.6903</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9125</v>
+        <v>0.0547</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.4391</v>
+        <v>-0.7451</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.4528</v>
+        <v>0.4136</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3499</v>
+        <v>-0.1825</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.1029</v>
+        <v>0.596</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5225</v>
+        <v>0.2175</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5225</v>
+        <v>0.2175</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6388</v>
+        <v>-0.1229</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.1622</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6472</v>
+        <v>0.0394</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.13</v>
+        <v>-0.1952</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.13</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. SOLA IDRISU</t>
+          <t>L. GIOVANNETTI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3966</v>
+        <v>-0.4065</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9643</v>
+        <v>0.1297</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5677</v>
+        <v>-0.5363</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2768</v>
+        <v>-0.9794</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1277</v>
+        <v>0.5626</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.149</v>
+        <v>-1.5419</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6903</v>
+        <v>0.4734</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0547</v>
+        <v>0.9125</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7451</v>
+        <v>-0.4391</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4136</v>
+        <v>-1.4528</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1825</v>
+        <v>-0.3499</v>
       </c>
       <c r="O18" t="n">
-        <v>0.596</v>
+        <v>-1.1029</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2175</v>
+        <v>1.5225</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2175</v>
+        <v>1.5225</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1422</v>
+        <v>0.1803</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.274</v>
+        <v>-0.3437</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1318</v>
+        <v>0.5239</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1952</v>
+        <v>-1.13</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1952</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6565</v>
+        <v>-0.4407</v>
       </c>
       <c r="E19" t="n">
         <v>3.6679</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.3244</v>
+        <v>-4.1087</v>
       </c>
       <c r="G19" t="n">
         <v>1.3551</v>
@@ -1936,13 +1936,13 @@
         <v>0.6525</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4041</v>
+        <v>-0.1884</v>
       </c>
       <c r="T19" t="n">
         <v>0.1971</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6012</v>
+        <v>-0.3854</v>
       </c>
       <c r="V19" t="n">
         <v>-2.2599</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3738</v>
+        <v>-1.8747</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1699</v>
+        <v>-1.3934</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2039</v>
+        <v>-0.4813</v>
       </c>
       <c r="G20" t="n">
         <v>-4.1707</v>
@@ -2014,13 +2014,13 @@
         <v>2.1751</v>
       </c>
       <c r="S20" t="n">
-        <v>1.3821</v>
+        <v>0.8811</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5997</v>
+        <v>0.3761</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7824</v>
+        <v>0.505</v>
       </c>
       <c r="V20" t="n">
         <v>-0.7602</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4388</v>
+        <v>-2.2404</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5098</v>
+        <v>-0.3843</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.9486</v>
+        <v>-1.8561</v>
       </c>
       <c r="G21" t="n">
         <v>-0.4703</v>
@@ -2092,13 +2092,13 @@
         <v>1.5225</v>
       </c>
       <c r="S21" t="n">
-        <v>1.3583</v>
+        <v>0.5567</v>
       </c>
       <c r="T21" t="n">
-        <v>1.5502</v>
+        <v>0.6561</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1919</v>
+        <v>-0.0994</v>
       </c>
       <c r="V21" t="n">
         <v>-1.6743</v>
@@ -2125,10 +2125,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.5082</v>
+        <v>-3.3964</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.2933</v>
+        <v>-2.1815</v>
       </c>
       <c r="F22" t="n">
         <v>-1.2148</v>
@@ -2170,10 +2170,10 @@
         <v>1.0875</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.149</v>
+        <v>-0.0373</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3425</v>
+        <v>-0.2307</v>
       </c>
       <c r="U22" t="n">
         <v>0.1935</v>
@@ -2203,19 +2203,19 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>14.6627</v>
+        <v>14.7144</v>
       </c>
       <c r="E23" t="n">
         <v>14.5786</v>
       </c>
       <c r="F23" t="n">
-        <v>0.08430000000000026</v>
+        <v>0.1355999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>7.574400000000001</v>
+        <v>7.574399999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.07530000000000037</v>
+        <v>-0.07530000000000014</v>
       </c>
       <c r="I23" t="n">
         <v>7.649899999999999</v>
@@ -2248,16 +2248,16 @@
         <v>19.5755</v>
       </c>
       <c r="S23" t="n">
-        <v>4.6926</v>
+        <v>4.744</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6009000000000001</v>
+        <v>0.6009</v>
       </c>
       <c r="U23" t="n">
-        <v>4.0916</v>
+        <v>4.1433</v>
       </c>
       <c r="V23" t="n">
-        <v>-4.129499999999999</v>
+        <v>-4.1295</v>
       </c>
       <c r="W23" t="n">
         <v>6.2562</v>
